--- a/basedatos_partidas/salida/descompuestos/10.02.02.060.xlsx
+++ b/basedatos_partidas/salida/descompuestos/10.02.02.060.xlsx
@@ -541,7 +541,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>MT-SOPORTE-AC</t>
+          <t>MT-SOPORTE-ANTIVIB</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -551,17 +551,17 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Soporte metálico galvanizado para unidad condensadora, con sus anclajes.</t>
+          <t>Soporte antivibratorio de neopreno (silent block) para aislar equipos de bombas, compresores y maquinaria, con su tornillería.</t>
         </is>
       </c>
       <c r="F10" t="n">
         <v>4</v>
       </c>
       <c r="G10" t="n">
-        <v>16</v>
+        <v>5</v>
       </c>
       <c r="H10" t="n">
-        <v>64</v>
+        <v>20</v>
       </c>
     </row>
     <row r="11">
@@ -597,7 +597,7 @@
         </is>
       </c>
       <c r="H12" t="n">
-        <v>72.8</v>
+        <v>28.8</v>
       </c>
     </row>
     <row r="13">
@@ -743,10 +743,10 @@
         <v>1</v>
       </c>
       <c r="G21" t="n">
-        <v>77.43000000000001</v>
+        <v>33.43</v>
       </c>
       <c r="H21" t="n">
-        <v>0.77</v>
+        <v>0.33</v>
       </c>
     </row>
     <row r="22">
@@ -762,7 +762,7 @@
       </c>
       <c r="G22" s="4" t="n"/>
       <c r="H22" s="5" t="n">
-        <v>78.2</v>
+        <v>33.76</v>
       </c>
     </row>
   </sheetData>
